--- a/backlogpo/product_backlog_team.xlsx
+++ b/backlogpo/product_backlog_team.xlsx
@@ -9,16 +9,17 @@
   <sheets>
     <sheet name="📋 Cover" sheetId="1" r:id="rId1"/>
     <sheet name="📌 Product Backlog" sheetId="2" r:id="rId2"/>
-    <sheet name="🗓 Sprint Planning" sheetId="3" r:id="rId3"/>
-    <sheet name="✅ Definition of Done" sheetId="4" r:id="rId4"/>
-    <sheet name="🗂 Kanban Board" sheetId="5" r:id="rId5"/>
+    <sheet name="🔄 Vận hành" sheetId="3" r:id="rId3"/>
+    <sheet name="🗓 Sprint Planning" sheetId="4" r:id="rId4"/>
+    <sheet name="✅ Definition of Done" sheetId="5" r:id="rId5"/>
+    <sheet name="🗂 Kanban Board" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="363">
   <si>
     <t>PRODUCT BACKLOG — ĐỘI PRODUCT</t>
   </si>
@@ -62,28 +63,25 @@
     <t>Draft</t>
   </si>
   <si>
-    <t>Tổng Epic</t>
-  </si>
-  <si>
-    <t>5 Epics</t>
-  </si>
-  <si>
-    <t>Tổng US</t>
-  </si>
-  <si>
-    <t>19 User Stories</t>
-  </si>
-  <si>
-    <t>Tổng SP</t>
-  </si>
-  <si>
-    <t>75 Story Points</t>
-  </si>
-  <si>
-    <t>Sprints</t>
-  </si>
-  <si>
-    <t>4 sprints (Release v1)</t>
+    <t>Tổng User Stories</t>
+  </si>
+  <si>
+    <t>Tổng Epics</t>
+  </si>
+  <si>
+    <t>Tổng Story Points (US)</t>
+  </si>
+  <si>
+    <t>Tổng Task Vận hành</t>
+  </si>
+  <si>
+    <t>In Progress (Vận hành)</t>
+  </si>
+  <si>
+    <t>To Do (Vận hành)</t>
+  </si>
+  <si>
+    <t>* Các ô màu cam tự động cập nhật khi thêm/sửa dữ liệu trong sheet Product Backlog và Vận hành.</t>
   </si>
   <si>
     <t>PRODUCT BACKLOG — HỆ THỐNG QUẢN LÝ TASK | ĐỘI PRODUCT</t>
@@ -104,7 +102,7 @@
     <t>US Title</t>
   </si>
   <si>
-    <t>User Story (As a / I want / So that)</t>
+    <t>User Story (As a/I want/So that)</t>
   </si>
   <si>
     <t>Acceptance Criteria (Gherkin)</t>
@@ -473,6 +471,9 @@
     <t>Sprint 5+</t>
   </si>
   <si>
+    <t>TỔNG</t>
+  </si>
+  <si>
     <t>MoSCoW:</t>
   </si>
   <si>
@@ -488,7 +489,512 @@
     <t>Won't Have v1</t>
   </si>
   <si>
-    <t>Tổng: 70 Story Points | 19 User Stories | 5 Epics</t>
+    <t>TASK VẬN HÀNH — Import từ Backlog FPTvn &amp; Roadmap 18.5  |  Loại trừ: Done</t>
+  </si>
+  <si>
+    <t>Nguồn</t>
+  </si>
+  <si>
+    <t>Tên Task</t>
+  </si>
+  <si>
+    <t>Mô tả yêu cầu</t>
+  </si>
+  <si>
+    <t>Sản phẩm</t>
+  </si>
+  <si>
+    <t>URL liên quan</t>
+  </si>
+  <si>
+    <t>Timeline</t>
+  </si>
+  <si>
+    <t>Ưu tiên</t>
+  </si>
+  <si>
+    <t>PIC Ecom</t>
+  </si>
+  <si>
+    <t>PIC Thực hiện</t>
+  </si>
+  <si>
+    <t>Ghi chú</t>
+  </si>
+  <si>
+    <t>OP-001</t>
+  </si>
+  <si>
+    <t>Backlog FPTvn</t>
+  </si>
+  <si>
+    <t>Hiển thị giá cloud camera</t>
+  </si>
+  <si>
+    <t>Không chia giá cloud theo mắt camera → Hiển thị giá buffet cloud 50.000đ/tháng. Cho khách chọn gói cloud theo kỳ.</t>
+  </si>
+  <si>
+    <t>Camera</t>
+  </si>
+  <si>
+    <t>https://fpt.vn/shop/camera/payment</t>
+  </si>
+  <si>
+    <t>15/4</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Nhờ Hà check với chị Linh</t>
+  </si>
+  <si>
+    <t>OP-002</t>
+  </si>
+  <si>
+    <t>Trang thanh toán Camera — gói cloud 3D buffet</t>
+  </si>
+  <si>
+    <t>Bỏ 'x5' trên gói cloud 3D buffet 6 tháng. Khi KH chọn tự lắp đặt → không hiển thị phí lắp.</t>
+  </si>
+  <si>
+    <t>ThuyTT104</t>
+  </si>
+  <si>
+    <t>In Progress</t>
+  </si>
+  <si>
+    <t>Đang làm việc với chính sách</t>
+  </si>
+  <si>
+    <t>OP-003</t>
+  </si>
+  <si>
+    <t>Update page local theo UI mới</t>
+  </si>
+  <si>
+    <t>Local pages và goi-dich-vu đang là source cũ → không linh hoạt thêm/chỉnh sửa section. Cần chuẩn hoá theo UI 2.0.</t>
+  </si>
+  <si>
+    <t>Internet</t>
+  </si>
+  <si>
+    <t>https://fpt.vn/lap-internet-wifi-hcm</t>
+  </si>
+  <si>
+    <t>24/4</t>
+  </si>
+  <si>
+    <t>Anhtd55</t>
+  </si>
+  <si>
+    <t>Local: add section rồi; Breadcrumbs chưa; Heading 1 chưa</t>
+  </si>
+  <si>
+    <t>OP-004</t>
+  </si>
+  <si>
+    <t>Luồng nâng cấp 5 dịch vụ</t>
+  </si>
+  <si>
+    <t>Nâng cấp VVIP, Camera, AP, băng thông, wifi6 bổ sung. Mapping chính sách nâng cấp.</t>
+  </si>
+  <si>
+    <t>/nang-cap</t>
+  </si>
+  <si>
+    <t>LongNH156</t>
+  </si>
+  <si>
+    <t>OP-005</t>
+  </si>
+  <si>
+    <t>LDP FCM</t>
+  </si>
+  <si>
+    <t>Landing page FCM — 22/5 golive 2 LDP.</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>22/5 là golive 2 LDP</t>
+  </si>
+  <si>
+    <t>OP-006</t>
+  </si>
+  <si>
+    <t>CMS Tổng đài wifi — 5 mẫu LDP</t>
+  </si>
+  <si>
+    <t>Thiết kế &amp; cấu hình 5 mẫu LDP trên CMS cho tổng đài wifi.</t>
+  </si>
+  <si>
+    <t>DoanhCN</t>
+  </si>
+  <si>
+    <t>OP-007</t>
+  </si>
+  <si>
+    <t>LDP nâng cấp — bổ sung luồng giao hàng Camera</t>
+  </si>
+  <si>
+    <t>Bổ sung luồng giao hàng cho Camera trên LDP nâng cấp.</t>
+  </si>
+  <si>
+    <t>26/5</t>
+  </si>
+  <si>
+    <t>OP-008</t>
+  </si>
+  <si>
+    <t>LDP FCitizen</t>
+  </si>
+  <si>
+    <t>LDP dành riêng cho FPTers. Chờ FTQ phản hồi quy trình bán gói.</t>
+  </si>
+  <si>
+    <t>SonLN11</t>
+  </si>
+  <si>
+    <t>Chờ FTQ phản hồi quy trình bán gói dành riêng cho FPTers</t>
+  </si>
+  <si>
+    <t>OP-009</t>
+  </si>
+  <si>
+    <t>Exit-intent popup trang Camera</t>
+  </si>
+  <si>
+    <t>Trigger desktop: mouse move back vào logo/breadcrumb/nav. Trigger mobile: scroll up nhanh.</t>
+  </si>
+  <si>
+    <t>/camera
+/camera/*</t>
+  </si>
+  <si>
+    <t>06/08/2026</t>
+  </si>
+  <si>
+    <t>OP-010</t>
+  </si>
+  <si>
+    <t>API Giá Vàng &amp; Điểm thi Đại học (Always-on)</t>
+  </si>
+  <si>
+    <t>Tích hợp API giá vàng SJC/9999 realtime. Widget hiển thị giá. Tích hợp API điểm thi ĐH.</t>
+  </si>
+  <si>
+    <t>06/06/2026</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>Không ưu tiên giai đoạn này</t>
+  </si>
+  <si>
+    <t>OP-011</t>
+  </si>
+  <si>
+    <t>Trang Author Profile Chuyên gia Camera</t>
+  </si>
+  <si>
+    <t>URL: /tac-gia/chuyen-gia-ky-thuat. Hiển thị 3-5 expert profile: ảnh thực, tên, chức vụ, chứng chỉ.</t>
+  </si>
+  <si>
+    <t>/tac-gia/chuyen-gia-ky-thuat</t>
+  </si>
+  <si>
+    <t>19/06</t>
+  </si>
+  <si>
+    <t>OP-012</t>
+  </si>
+  <si>
+    <t>LDP Ngoại Hạng Anh (NHA)</t>
+  </si>
+  <si>
+    <t>LP tổng hợp: Kết quả trận đấu, Bảng xếp hạng cập nhật tự động qua API. 2 layout intent kết quả NHA.</t>
+  </si>
+  <si>
+    <t>Internet/SA</t>
+  </si>
+  <si>
+    <t>https://fpt.vn/ngoai-hang-anh/lich-thi-dau</t>
+  </si>
+  <si>
+    <t>20/06/2026</t>
+  </si>
+  <si>
+    <t>OP-013</t>
+  </si>
+  <si>
+    <t>Video Hub (FPT Play)</t>
+  </si>
+  <si>
+    <t>Block video tự động lấy nguồn từ YouTube FPT Play (Recap/Highlight). Schema VideoObject, lazy-load, responsive.</t>
+  </si>
+  <si>
+    <t>https://fpt.vn/ngoai-hang-anh</t>
+  </si>
+  <si>
+    <t>27/06/2026</t>
+  </si>
+  <si>
+    <t>OP-014</t>
+  </si>
+  <si>
+    <t>Structured Data Schema cho nội dung SEO</t>
+  </si>
+  <si>
+    <t>Triển khai JSON-LD: Article, BreadcrumbList, FAQPage, Product. Tool kiểm tra: Google Rich Results.</t>
+  </si>
+  <si>
+    <t>03/06/2026</t>
+  </si>
+  <si>
+    <t>OP-015</t>
+  </si>
+  <si>
+    <t>Core Web Vitals — cải thiện LCP/CLS</t>
+  </si>
+  <si>
+    <t>LCP &lt; 2.5s, CLS &lt; 0.1. Tối ưu images (WebP/AVIF), preload critical CSS, giảm layout shift.</t>
+  </si>
+  <si>
+    <t>OP-016</t>
+  </si>
+  <si>
+    <t>Luồng mua mới Camera — bổ sung giỏ hàng</t>
+  </si>
+  <si>
+    <t>BA đánh giá xây dựng thêm luồng hướng dẫn. Không mua cùng lúc 1 cam ngoài trời + 1 cam trong nhà → bổ sung giỏ hàng.</t>
+  </si>
+  <si>
+    <t>24/06/2026</t>
+  </si>
+  <si>
+    <t>Bổ sung thêm luồng giỏ hàng — đã bsung vào Backlog</t>
+  </si>
+  <si>
+    <t>OP-017</t>
+  </si>
+  <si>
+    <t>Luồng Mua mới Camera — đứt gãy tại bước Thanh toán</t>
+  </si>
+  <si>
+    <t>Thao tác mua mới Camera Play bị đứt gãy tại bước Thanh toán. Cần fix flow.</t>
+  </si>
+  <si>
+    <t>OP-018</t>
+  </si>
+  <si>
+    <t>Luồng Mua mới Camera — fix combo</t>
+  </si>
+  <si>
+    <t>Không mua cùng lúc 1 cam ngoài trời và 1 cam trong nhà → bổ sung giỏ hàng combo.</t>
+  </si>
+  <si>
+    <t>RM-001</t>
+  </si>
+  <si>
+    <t>Roadmap 18.5</t>
+  </si>
+  <si>
+    <t>Luồng bán Camera chỉ giao hàng: Sàn TMĐT</t>
+  </si>
+  <si>
+    <t>Luồng bán Camera chỉ giao hàng trên Sàn TMĐT. Chưa có chỗ nâng cấp Camera combo trên HD net only.</t>
+  </si>
+  <si>
+    <t>Sàn TMĐT</t>
+  </si>
+  <si>
+    <t>20/6</t>
+  </si>
+  <si>
+    <t>Anh LongNH158</t>
+  </si>
+  <si>
+    <t>Chưa có chỗ nâng cấp camera combo trên HD net only</t>
+  </si>
+  <si>
+    <t>RM-002</t>
+  </si>
+  <si>
+    <t>LDP FCitizen — UI/UX &amp; chính sách gói bán</t>
+  </si>
+  <si>
+    <t>Thiết kế UI/UX LDP FCitizen và cập nhật chính sách/gói bán &amp; verify thông tin theo chính sách tháng.</t>
+  </si>
+  <si>
+    <t>https://fcitizen.fpt.vn/ → fpt.vn/fcitizen</t>
+  </si>
+  <si>
+    <t>06/03/2026</t>
+  </si>
+  <si>
+    <t>Anh Thuận</t>
+  </si>
+  <si>
+    <t>Rồi sẽ bán thế nào? hay chỉ sửa UI LDP?</t>
+  </si>
+  <si>
+    <t>RM-003</t>
+  </si>
+  <si>
+    <t>Luồng nâng cấp 5 Dịch vụ - FPT.vn</t>
+  </si>
+  <si>
+    <t>Thiết kế UI/UX, map chính sách nâng cấp 5 dịch vụ trên website FPT.vn.</t>
+  </si>
+  <si>
+    <t>Nâng cấp/ bán thêm</t>
+  </si>
+  <si>
+    <t>FPT.vn</t>
+  </si>
+  <si>
+    <t>30/6</t>
+  </si>
+  <si>
+    <t>Anh ManhDT3</t>
+  </si>
+  <si>
+    <t>RM-004</t>
+  </si>
+  <si>
+    <t>Hub vinh danh Giới thiệu bạn bè trên App HiFPT</t>
+  </si>
+  <si>
+    <t>Tạo mục vinh danh KH Giới thiệu bạn bè: Level Cơ bản, Bạc, Vàng, Kim cương.</t>
+  </si>
+  <si>
+    <t>Giới thiệu bạn bè</t>
+  </si>
+  <si>
+    <t>HiFPT</t>
+  </si>
+  <si>
+    <t>LinhTT119</t>
+  </si>
+  <si>
+    <t>Chị Tuyết Vũ HiFPT</t>
+  </si>
+  <si>
+    <t>RM-005</t>
+  </si>
+  <si>
+    <t>LDP Giới thiệu bạn bè — Người được giới thiệu</t>
+  </si>
+  <si>
+    <t>LDP điều hướng KH được giới thiệu vào mua toàn bộ sản phẩm FPT qua chương trình GTBB.</t>
+  </si>
+  <si>
+    <t>30/7</t>
+  </si>
+  <si>
+    <t>Anh Thuận &amp; Anh Tài</t>
+  </si>
+  <si>
+    <t>RM-006</t>
+  </si>
+  <si>
+    <t>Tích hợp Auto Pay trên website FPT.vn</t>
+  </si>
+  <si>
+    <t>Tích hợp luồng tự động lưu thẻ và thanh toán định kỳ cho KH mua Dịch vụ trên website FPT.vn.</t>
+  </si>
+  <si>
+    <t>Thanh toán</t>
+  </si>
+  <si>
+    <t>Cần làm rõ kịch bản thanh toán auto pay</t>
+  </si>
+  <si>
+    <t>RM-007</t>
+  </si>
+  <si>
+    <t>Gửi E-Card khi mua gói SA Play trên FPT.vn &amp; HiFPT</t>
+  </si>
+  <si>
+    <t>Khi KH mua gói SA Play, lựa chọn hình thức 'KH nhận mã và tự kích hoạt' → gửi E-Card cho bạn bè.</t>
+  </si>
+  <si>
+    <t>SA Play</t>
+  </si>
+  <si>
+    <t>FPT.vn &amp; HiFPT</t>
+  </si>
+  <si>
+    <t>ISC đánh dấu KH đi theo luồng nhận mã; FPL trả thông tin qua ZNS</t>
+  </si>
+  <si>
+    <t>RM-008</t>
+  </si>
+  <si>
+    <t>Landing Page Camera GenZ</t>
+  </si>
+  <si>
+    <t>Thiết kế UI/UX LDP Camera GenZ. Mapping &amp; config gói bán &amp; chính sách.</t>
+  </si>
+  <si>
+    <t>Đánh giá lại mức độ ưu tiên → owner?</t>
+  </si>
+  <si>
+    <t>RM-009</t>
+  </si>
+  <si>
+    <t>Luồng Recall</t>
+  </si>
+  <si>
+    <t>Kênh bán: FPT.vn &amp; HiFPT. Sản phẩm: Internet Only, Combo Internet+Phim, Camera.</t>
+  </si>
+  <si>
+    <t>RM-010</t>
+  </si>
+  <si>
+    <t>Luồng Autocall — tích hợp ZNS</t>
+  </si>
+  <si>
+    <t>Tích hợp ZNS cho Autocall tệp KH hiện hữu — Nâng cấp/bán thêm dịch vụ.</t>
+  </si>
+  <si>
+    <t>RM-011</t>
+  </si>
+  <si>
+    <t>Cross-sell FPTPlay.vn</t>
+  </si>
+  <si>
+    <t>Xây dựng luồng cross-sell từ FPT.vn sang FPTPlay.vn.</t>
+  </si>
+  <si>
+    <t>RM-012</t>
+  </si>
+  <si>
+    <t>Self-Service Cam trên sàn TMĐT</t>
+  </si>
+  <si>
+    <t>Triển khai Self-Service Camera trên các sàn TMĐT (Shopee, Lazada, Tiki).</t>
+  </si>
+  <si>
+    <t>RM-013</t>
+  </si>
+  <si>
+    <t>Chính sách GTBB tặng thiết bị Cam &amp; Cloud</t>
+  </si>
+  <si>
+    <t>Áp dụng chính sách Giới Thiệu Bạn Bè tặng kèm thiết bị Camera và gói Cloud.</t>
+  </si>
+  <si>
+    <t>RM-014</t>
+  </si>
+  <si>
+    <t>(Task chưa đặt tên — cần bổ sung)</t>
+  </si>
+  <si>
+    <t>Task chưa có tên và mô tả. Cần PO xác nhận.</t>
   </si>
   <si>
     <t>SPRINT PLANNING — RELEASE v1</t>
@@ -552,9 +1058,6 @@
   </si>
   <si>
     <t>Burn-down chart, retrospective, team dashboard, notifications</t>
-  </si>
-  <si>
-    <t>06/08/2026</t>
   </si>
   <si>
     <t>19/08/2026</t>
@@ -678,23 +1181,12 @@
 Đặt độ ưu tiên &amp; deadline</t>
   </si>
   <si>
-    <t>US-005
-Tìm kiếm &amp; lọc task</t>
-  </si>
-  <si>
-    <t>US-006
-Comment &amp; đính kèm file trên task</t>
-  </si>
-  <si>
     <t>US-007
 Tạo và quản lý Sprint</t>
   </si>
   <si>
-    <t>US-008
-Thêm task vào Sprint</t>
-  </si>
-  <si>
-    <t>In Progress</t>
+    <t>US-015
+Quản lý vai trò thành viên</t>
   </si>
   <si>
     <t>Review</t>
@@ -707,7 +1199,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="16">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -739,6 +1231,19 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFE86A23"/>
+      <name val="Times New Roman"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF888888"/>
       <name val="Times New Roman"/>
       <family val="2"/>
     </font>
@@ -779,7 +1284,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF888888"/>
+      <color rgb="FF1E4D8C"/>
       <name val="Times New Roman"/>
       <family val="2"/>
     </font>
@@ -791,8 +1296,36 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF888888"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFC0392B"/>
+      <name val="Times New Roman"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFE67E22"/>
+      <name val="Times New Roman"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFAAAAAA"/>
+      <name val="Times New Roman"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF27AE60"/>
+      <name val="Times New Roman"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF6C3483"/>
       <name val="Times New Roman"/>
       <family val="2"/>
     </font>
@@ -816,7 +1349,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="19">
+  <fills count="24">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -837,13 +1370,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFF0E8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF1F2737"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0F0F0"/>
+        <fgColor rgb="FFEBF5FB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -868,6 +1407,42 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF95A5A6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0F7FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8F4FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEF9E7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5EEF8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8F0FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0E8FF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -909,18 +1484,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFEF9E7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEBF5FB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFEAFAF1"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -951,16 +1514,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFCCCCCC"/>
+        <color rgb="FFBBBBBB"/>
       </left>
       <right style="thin">
-        <color rgb="FFCCCCCC"/>
+        <color rgb="FFBBBBBB"/>
       </right>
       <top style="thin">
-        <color rgb="FFCCCCCC"/>
+        <color rgb="FFBBBBBB"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFCCCCCC"/>
+        <color rgb="FFBBBBBB"/>
       </bottom>
       <diagonal/>
     </border>
@@ -998,7 +1561,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1013,121 +1576,178 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1424,14 +2044,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="B3:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="3.7109375" customWidth="1"/>
     <col min="2" max="7" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" ht="20" customHeight="1"/>
     <row r="3" spans="2:7" ht="45" customHeight="1">
       <c r="B3" s="1" t="s">
         <v>0</v>
@@ -1442,7 +2061,7 @@
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
     </row>
-    <row r="4" spans="2:7" ht="30" customHeight="1">
+    <row r="4" spans="2:7" ht="28" customHeight="1">
       <c r="B4" s="2" t="s">
         <v>1</v>
       </c>
@@ -1460,7 +2079,6 @@
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
     </row>
-    <row r="8" spans="2:7" ht="22" customHeight="1"/>
     <row r="9" spans="2:7" ht="22" customHeight="1">
       <c r="B9" s="4" t="s">
         <v>2</v>
@@ -1509,40 +2127,72 @@
       </c>
       <c r="G11" s="5"/>
     </row>
-    <row r="12" spans="2:7" ht="22" customHeight="1">
+    <row r="12" spans="2:7" ht="26" customHeight="1">
       <c r="B12" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="6">
+        <f>COUNTA('📌 Product Backlog'!B4:B1000)+COUNTA('🔄 Vận hành'!A4:A1000)</f>
+        <v>0</v>
+      </c>
+      <c r="D12" s="6"/>
+      <c r="E12" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="5"/>
-      <c r="E12" s="4" t="s">
+      <c r="F12" s="6">
+        <f>SUMPRODUCT(1/COUNTIF('📌 Product Backlog'!C4:C22,'📌 Product Backlog'!C4:C22))</f>
+        <v>0</v>
+      </c>
+      <c r="G12" s="6"/>
+    </row>
+    <row r="13" spans="2:7" ht="26" customHeight="1">
+      <c r="B13" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="C13" s="6">
+        <f>SUM('📌 Product Backlog'!H4:H22)</f>
+        <v>0</v>
+      </c>
+      <c r="D13" s="6"/>
+      <c r="E13" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G12" s="5"/>
-    </row>
-    <row r="13" spans="2:7">
-      <c r="B13" s="4" t="s">
+      <c r="F13" s="6">
+        <f>COUNTA('🔄 Vận hành'!A4:A1000)</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="6"/>
+    </row>
+    <row r="14" spans="2:7" ht="26" customHeight="1">
+      <c r="B14" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C14" s="6">
+        <f>COUNTIF('🔄 Vận hành'!K4:K35,"In Progress")</f>
+        <v>0</v>
+      </c>
+      <c r="D14" s="6"/>
+      <c r="E14" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D13" s="5"/>
-      <c r="E13" s="4" t="s">
+      <c r="F14" s="6">
+        <f>COUNTIF('🔄 Vận hành'!K4:K35,"To Do")</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="6"/>
+    </row>
+    <row r="16" spans="2:7">
+      <c r="B16" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="F13" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="G13" s="5"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="16">
     <mergeCell ref="B3:G3"/>
     <mergeCell ref="B4:G4"/>
     <mergeCell ref="B6:G6"/>
@@ -1556,6 +2206,9 @@
     <mergeCell ref="F12:G12"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="B16:G16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1563,716 +2216,1829 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4.7109375" customWidth="1"/>
     <col min="2" max="3" width="8.7109375" customWidth="1"/>
     <col min="4" max="4" width="14.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
-    <col min="6" max="6" width="38.7109375" customWidth="1"/>
-    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="6" max="7" width="38.7109375" customWidth="1"/>
     <col min="8" max="8" width="6.7109375" customWidth="1"/>
     <col min="9" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="32" customHeight="1">
-      <c r="A1" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
+      <c r="A1" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
     </row>
     <row r="2" spans="1:10" ht="28" customHeight="1"/>
     <row r="3" spans="1:10">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="C3" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="D3" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="E3" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="F3" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="G3" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="H3" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="I3" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="J3" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="J3" s="7" t="s">
+    </row>
+    <row r="4" spans="1:10" ht="90" customHeight="1">
+      <c r="A4" s="10">
+        <v>1</v>
+      </c>
+      <c r="B4" s="11" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" ht="90" customHeight="1">
-      <c r="A4" s="8">
-        <v>1</v>
-      </c>
-      <c r="B4" s="9" t="s">
+      <c r="C4" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="D4" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="E4" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="F4" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="G4" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="H4" s="15">
+        <v>3</v>
+      </c>
+      <c r="I4" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="H4" s="13">
+      <c r="J4" s="16" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="90" customHeight="1">
+      <c r="A5" s="17">
+        <v>2</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="F5" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="G5" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="H5" s="21">
         <v>3</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="I5" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="J5" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="J4" s="14" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="90" customHeight="1">
-      <c r="A5" s="15">
+    </row>
+    <row r="6" spans="1:10" ht="90" customHeight="1">
+      <c r="A6" s="10">
+        <v>3</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="G6" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="H6" s="15">
         <v>2</v>
       </c>
-      <c r="B5" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="C5" s="17" t="s">
+      <c r="I6" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="J6" s="16" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="90" customHeight="1">
+      <c r="A7" s="17">
+        <v>4</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="D5" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="E5" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="F5" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="G5" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="H5" s="19">
+      <c r="E7" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="F7" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="G7" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="H7" s="21">
+        <v>2</v>
+      </c>
+      <c r="I7" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="J7" s="16" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="90" customHeight="1">
+      <c r="A8" s="10">
+        <v>5</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="G8" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="H8" s="15">
         <v>3</v>
       </c>
-      <c r="I5" s="15" t="s">
+      <c r="I8" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="J8" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="J5" s="14" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="90" customHeight="1">
-      <c r="A6" s="8">
+    </row>
+    <row r="9" spans="1:10" ht="90" customHeight="1">
+      <c r="A9" s="17">
+        <v>6</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="F9" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="G9" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="H9" s="21">
         <v>3</v>
       </c>
-      <c r="B6" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="F6" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="G6" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="H6" s="13">
-        <v>2</v>
-      </c>
-      <c r="I6" s="8" t="s">
+      <c r="I9" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="J9" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="14" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="90" customHeight="1">
-      <c r="A7" s="15">
-        <v>4</v>
-      </c>
-      <c r="B7" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="C7" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="D7" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="F7" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="G7" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="H7" s="19">
-        <v>2</v>
-      </c>
-      <c r="I7" s="15" t="s">
+    </row>
+    <row r="10" spans="1:10" ht="90" customHeight="1">
+      <c r="A10" s="10">
+        <v>7</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="G10" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="H10" s="15">
+        <v>3</v>
+      </c>
+      <c r="I10" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="J10" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="J7" s="14" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="90" customHeight="1">
-      <c r="A8" s="8">
+    </row>
+    <row r="11" spans="1:10" ht="90" customHeight="1">
+      <c r="A11" s="17">
+        <v>8</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="F11" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="G11" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="H11" s="21">
+        <v>3</v>
+      </c>
+      <c r="I11" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="J11" s="16" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="90" customHeight="1">
+      <c r="A12" s="10">
+        <v>9</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="G12" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="H12" s="15">
         <v>5</v>
       </c>
-      <c r="B8" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="E8" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="F8" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="G8" s="11" t="s">
+      <c r="I12" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="J12" s="16" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="90" customHeight="1">
+      <c r="A13" s="17">
+        <v>10</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="D13" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="F13" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="G13" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="H13" s="21">
+        <v>3</v>
+      </c>
+      <c r="I13" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="J13" s="16" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="90" customHeight="1">
+      <c r="A14" s="10">
+        <v>11</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="E14" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="F14" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="G14" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="H14" s="15">
+        <v>3</v>
+      </c>
+      <c r="I14" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="H8" s="13">
+      <c r="J14" s="16" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="90" customHeight="1">
+      <c r="A15" s="17">
+        <v>12</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="D15" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="E15" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="F15" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="G15" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="H15" s="21">
+        <v>5</v>
+      </c>
+      <c r="I15" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="J15" s="16" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="90" customHeight="1">
+      <c r="A16" s="10">
+        <v>13</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="F16" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="G16" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="H16" s="15">
+        <v>5</v>
+      </c>
+      <c r="I16" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="J16" s="16" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="90" customHeight="1">
+      <c r="A17" s="17">
+        <v>14</v>
+      </c>
+      <c r="B17" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="C17" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="D17" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="E17" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="F17" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="G17" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="H17" s="21">
+        <v>5</v>
+      </c>
+      <c r="I17" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="J17" s="16" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="90" customHeight="1">
+      <c r="A18" s="10">
+        <v>15</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="E18" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="F18" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="G18" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="H18" s="15">
         <v>3</v>
       </c>
-      <c r="I8" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="J8" s="14" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="90" customHeight="1">
-      <c r="A9" s="15">
-        <v>6</v>
-      </c>
-      <c r="B9" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="C9" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="E9" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="F9" s="18" t="s">
-        <v>60</v>
-      </c>
-      <c r="G9" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="H9" s="19">
+      <c r="I18" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="J18" s="16" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="90" customHeight="1">
+      <c r="A19" s="17">
+        <v>16</v>
+      </c>
+      <c r="B19" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="C19" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="D19" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="E19" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="F19" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="G19" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="H19" s="21">
         <v>3</v>
       </c>
-      <c r="I9" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="J9" s="14" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="90" customHeight="1">
-      <c r="A10" s="8">
-        <v>7</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="F10" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="G10" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="H10" s="13">
+      <c r="I19" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="J19" s="16" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="90" customHeight="1">
+      <c r="A20" s="10">
+        <v>17</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="E20" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="F20" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="G20" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="H20" s="15">
         <v>3</v>
       </c>
-      <c r="I10" s="8" t="s">
+      <c r="I20" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="J20" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="J10" s="14" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="90" customHeight="1">
-      <c r="A11" s="15">
+    </row>
+    <row r="21" spans="1:10" ht="90" customHeight="1">
+      <c r="A21" s="17">
+        <v>18</v>
+      </c>
+      <c r="B21" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="C21" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="D21" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="E21" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="F21" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="G21" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="H21" s="21">
+        <v>5</v>
+      </c>
+      <c r="I21" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="J21" s="16" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="90" customHeight="1">
+      <c r="A22" s="10">
+        <v>19</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="E22" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="F22" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="G22" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="H22" s="15">
         <v>8</v>
       </c>
-      <c r="B11" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="C11" s="17" t="s">
-        <v>63</v>
-      </c>
-      <c r="D11" s="18" t="s">
-        <v>64</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="F11" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="G11" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="H11" s="19">
-        <v>3</v>
-      </c>
-      <c r="I11" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="J11" s="14" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="90" customHeight="1">
-      <c r="A12" s="8">
-        <v>9</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="E12" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="F12" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="G12" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="H12" s="13">
-        <v>5</v>
-      </c>
-      <c r="I12" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="J12" s="14" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="90" customHeight="1">
-      <c r="A13" s="15">
-        <v>10</v>
-      </c>
-      <c r="B13" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="C13" s="17" t="s">
-        <v>63</v>
-      </c>
-      <c r="D13" s="18" t="s">
-        <v>64</v>
-      </c>
-      <c r="E13" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="F13" s="18" t="s">
-        <v>79</v>
-      </c>
-      <c r="G13" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="H13" s="19">
-        <v>3</v>
-      </c>
-      <c r="I13" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="J13" s="14" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="90" customHeight="1">
-      <c r="A14" s="8">
-        <v>11</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="D14" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="E14" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="F14" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="G14" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="H14" s="13">
-        <v>3</v>
-      </c>
-      <c r="I14" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="J14" s="14" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="90" customHeight="1">
-      <c r="A15" s="15">
-        <v>12</v>
-      </c>
-      <c r="B15" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="C15" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="D15" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="E15" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="F15" s="18" t="s">
-        <v>89</v>
-      </c>
-      <c r="G15" s="18" t="s">
-        <v>90</v>
-      </c>
-      <c r="H15" s="19">
-        <v>5</v>
-      </c>
-      <c r="I15" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="J15" s="14" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="90" customHeight="1">
-      <c r="A16" s="8">
-        <v>13</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="D16" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="E16" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="F16" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="G16" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="H16" s="13">
-        <v>5</v>
-      </c>
-      <c r="I16" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="J16" s="14" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="90" customHeight="1">
-      <c r="A17" s="15">
-        <v>14</v>
-      </c>
-      <c r="B17" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="C17" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="D17" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="E17" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="F17" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="G17" s="18" t="s">
-        <v>99</v>
-      </c>
-      <c r="H17" s="19">
-        <v>5</v>
-      </c>
-      <c r="I17" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="J17" s="14" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="90" customHeight="1">
-      <c r="A18" s="8">
-        <v>15</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="D18" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="E18" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="F18" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="G18" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="H18" s="13">
-        <v>3</v>
-      </c>
-      <c r="I18" s="8" t="s">
+      <c r="I22" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="J22" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="J18" s="14" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="90" customHeight="1">
-      <c r="A19" s="15">
-        <v>16</v>
-      </c>
-      <c r="B19" s="16" t="s">
-        <v>106</v>
-      </c>
-      <c r="C19" s="17" t="s">
-        <v>101</v>
-      </c>
-      <c r="D19" s="18" t="s">
-        <v>102</v>
-      </c>
-      <c r="E19" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="F19" s="18" t="s">
-        <v>108</v>
-      </c>
-      <c r="G19" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="H19" s="19">
-        <v>3</v>
-      </c>
-      <c r="I19" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="J19" s="14" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="90" customHeight="1">
-      <c r="A20" s="8">
-        <v>17</v>
-      </c>
-      <c r="B20" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="C20" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="D20" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="E20" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="F20" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="G20" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="H20" s="13">
-        <v>3</v>
-      </c>
-      <c r="I20" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="J20" s="14" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="90" customHeight="1">
-      <c r="A21" s="15">
-        <v>18</v>
-      </c>
-      <c r="B21" s="16" t="s">
-        <v>116</v>
-      </c>
-      <c r="C21" s="17" t="s">
-        <v>111</v>
-      </c>
-      <c r="D21" s="18" t="s">
-        <v>112</v>
-      </c>
-      <c r="E21" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="F21" s="18" t="s">
-        <v>118</v>
-      </c>
-      <c r="G21" s="18" t="s">
-        <v>119</v>
-      </c>
-      <c r="H21" s="19">
-        <v>5</v>
-      </c>
-      <c r="I21" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="J21" s="14" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="90" customHeight="1">
-      <c r="A22" s="8">
-        <v>19</v>
-      </c>
-      <c r="B22" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="C22" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="D22" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="E22" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="F22" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="G22" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="H22" s="13">
-        <v>8</v>
-      </c>
-      <c r="I22" s="8" t="s">
+    </row>
+    <row r="24" spans="1:10" ht="24" customHeight="1">
+      <c r="A24" s="22" t="s">
         <v>124</v>
       </c>
-      <c r="J22" s="14" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="14" customHeight="1">
-      <c r="A24" s="20"/>
-      <c r="B24" s="20"/>
-      <c r="C24" s="20"/>
-      <c r="D24" s="20"/>
-      <c r="E24" s="20"/>
-      <c r="F24" s="20"/>
-      <c r="G24" s="20"/>
-      <c r="H24" s="20"/>
-      <c r="I24" s="20"/>
-      <c r="J24" s="20"/>
-    </row>
-    <row r="25" spans="1:10" ht="22" customHeight="1">
-      <c r="A25" s="21" t="s">
+      <c r="B24" s="22"/>
+      <c r="C24" s="22"/>
+      <c r="D24" s="22"/>
+      <c r="E24" s="22"/>
+      <c r="F24" s="22"/>
+      <c r="G24" s="22"/>
+      <c r="H24" s="22">
+        <f>SUM(H4:H22)</f>
+        <v>0</v>
+      </c>
+      <c r="I24" s="22">
+        <f>COUNTA(I4:I22)&amp;" sprints"</f>
+        <v>0</v>
+      </c>
+      <c r="J24" s="22">
+        <f>COUNTA(J4:J22)&amp;" US"</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="22" customHeight="1">
+      <c r="A26" s="23" t="s">
         <v>125</v>
       </c>
-      <c r="B25" s="22" t="s">
+      <c r="B26" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="C25" s="23" t="s">
+      <c r="C26" s="25" t="s">
         <v>127</v>
       </c>
-      <c r="D25" s="24" t="s">
+      <c r="D26" s="26" t="s">
         <v>128</v>
       </c>
-      <c r="E25" s="25" t="s">
+      <c r="E26" s="27" t="s">
         <v>129</v>
-      </c>
-      <c r="F25" s="26" t="s">
-        <v>130</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="A24:G24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:L37"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="8.7109375" customWidth="1"/>
+    <col min="2" max="2" width="14.7109375" customWidth="1"/>
+    <col min="3" max="3" width="22.7109375" customWidth="1"/>
+    <col min="4" max="4" width="32.7109375" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" customWidth="1"/>
+    <col min="6" max="6" width="20.7109375" customWidth="1"/>
+    <col min="7" max="7" width="12.7109375" customWidth="1"/>
+    <col min="8" max="8" width="10.7109375" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" customWidth="1"/>
+    <col min="10" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="12.7109375" customWidth="1"/>
+    <col min="12" max="12" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="32" customHeight="1">
+      <c r="A1" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+    </row>
+    <row r="2" spans="1:12" ht="28" customHeight="1"/>
+    <row r="3" spans="1:12">
+      <c r="A3" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="75" customHeight="1">
+      <c r="A4" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="B4" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="C4" s="29" t="s">
+        <v>143</v>
+      </c>
+      <c r="D4" s="30" t="s">
+        <v>144</v>
+      </c>
+      <c r="E4" s="31" t="s">
+        <v>145</v>
+      </c>
+      <c r="F4" s="30" t="s">
+        <v>146</v>
+      </c>
+      <c r="G4" s="31" t="s">
+        <v>147</v>
+      </c>
+      <c r="H4" s="32" t="s">
+        <v>148</v>
+      </c>
+      <c r="I4" s="31"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="L4" s="30" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="75" customHeight="1">
+      <c r="A5" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="B5" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="C5" s="33" t="s">
+        <v>151</v>
+      </c>
+      <c r="D5" s="34" t="s">
+        <v>152</v>
+      </c>
+      <c r="E5" s="35" t="s">
+        <v>145</v>
+      </c>
+      <c r="F5" s="34" t="s">
+        <v>146</v>
+      </c>
+      <c r="G5" s="35" t="s">
+        <v>147</v>
+      </c>
+      <c r="H5" s="32" t="s">
+        <v>148</v>
+      </c>
+      <c r="I5" s="35" t="s">
+        <v>153</v>
+      </c>
+      <c r="J5" s="35"/>
+      <c r="K5" s="36" t="s">
+        <v>154</v>
+      </c>
+      <c r="L5" s="34" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="75" customHeight="1">
+      <c r="A6" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="B6" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="C6" s="29" t="s">
+        <v>157</v>
+      </c>
+      <c r="D6" s="30" t="s">
+        <v>158</v>
+      </c>
+      <c r="E6" s="31" t="s">
+        <v>159</v>
+      </c>
+      <c r="F6" s="30" t="s">
+        <v>160</v>
+      </c>
+      <c r="G6" s="31" t="s">
+        <v>161</v>
+      </c>
+      <c r="H6" s="32" t="s">
+        <v>148</v>
+      </c>
+      <c r="I6" s="31" t="s">
+        <v>162</v>
+      </c>
+      <c r="J6" s="31"/>
+      <c r="K6" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="L6" s="30" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="75" customHeight="1">
+      <c r="A7" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="B7" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="C7" s="33" t="s">
+        <v>165</v>
+      </c>
+      <c r="D7" s="34" t="s">
+        <v>166</v>
+      </c>
+      <c r="E7" s="35" t="s">
+        <v>159</v>
+      </c>
+      <c r="F7" s="34" t="s">
+        <v>167</v>
+      </c>
+      <c r="G7" s="35"/>
+      <c r="H7" s="32" t="s">
+        <v>148</v>
+      </c>
+      <c r="I7" s="35" t="s">
+        <v>168</v>
+      </c>
+      <c r="J7" s="35"/>
+      <c r="K7" s="36" t="s">
+        <v>154</v>
+      </c>
+      <c r="L7" s="34"/>
+    </row>
+    <row r="8" spans="1:12" ht="75" customHeight="1">
+      <c r="A8" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="B8" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="C8" s="29" t="s">
+        <v>170</v>
+      </c>
+      <c r="D8" s="30" t="s">
+        <v>171</v>
+      </c>
+      <c r="E8" s="31" t="s">
+        <v>159</v>
+      </c>
+      <c r="F8" s="30"/>
+      <c r="G8" s="31"/>
+      <c r="H8" s="37" t="s">
+        <v>172</v>
+      </c>
+      <c r="I8" s="31" t="s">
+        <v>168</v>
+      </c>
+      <c r="J8" s="31"/>
+      <c r="K8" s="36" t="s">
+        <v>154</v>
+      </c>
+      <c r="L8" s="30" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="75" customHeight="1">
+      <c r="A9" s="18" t="s">
+        <v>174</v>
+      </c>
+      <c r="B9" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="C9" s="33" t="s">
+        <v>175</v>
+      </c>
+      <c r="D9" s="34" t="s">
+        <v>176</v>
+      </c>
+      <c r="E9" s="35"/>
+      <c r="F9" s="34"/>
+      <c r="G9" s="35"/>
+      <c r="H9" s="32" t="s">
+        <v>148</v>
+      </c>
+      <c r="I9" s="35" t="s">
+        <v>177</v>
+      </c>
+      <c r="J9" s="35"/>
+      <c r="K9" s="38"/>
+      <c r="L9" s="34"/>
+    </row>
+    <row r="10" spans="1:12" ht="75" customHeight="1">
+      <c r="A10" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="B10" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="C10" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="D10" s="30" t="s">
+        <v>180</v>
+      </c>
+      <c r="E10" s="31"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="31" t="s">
+        <v>181</v>
+      </c>
+      <c r="H10" s="32" t="s">
+        <v>148</v>
+      </c>
+      <c r="I10" s="31" t="s">
+        <v>153</v>
+      </c>
+      <c r="J10" s="31"/>
+      <c r="K10" s="36" t="s">
+        <v>154</v>
+      </c>
+      <c r="L10" s="30"/>
+    </row>
+    <row r="11" spans="1:12" ht="75" customHeight="1">
+      <c r="A11" s="18" t="s">
+        <v>182</v>
+      </c>
+      <c r="B11" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="C11" s="33" t="s">
+        <v>183</v>
+      </c>
+      <c r="D11" s="34" t="s">
+        <v>184</v>
+      </c>
+      <c r="E11" s="35"/>
+      <c r="F11" s="34"/>
+      <c r="G11" s="35"/>
+      <c r="H11" s="32" t="s">
+        <v>148</v>
+      </c>
+      <c r="I11" s="35" t="s">
+        <v>185</v>
+      </c>
+      <c r="J11" s="35"/>
+      <c r="K11" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="L11" s="34" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="75" customHeight="1">
+      <c r="A12" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B12" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="C12" s="29" t="s">
+        <v>188</v>
+      </c>
+      <c r="D12" s="30" t="s">
+        <v>189</v>
+      </c>
+      <c r="E12" s="31" t="s">
+        <v>145</v>
+      </c>
+      <c r="F12" s="30" t="s">
+        <v>190</v>
+      </c>
+      <c r="G12" s="31" t="s">
+        <v>191</v>
+      </c>
+      <c r="H12" s="32" t="s">
+        <v>148</v>
+      </c>
+      <c r="I12" s="31" t="s">
+        <v>185</v>
+      </c>
+      <c r="J12" s="31"/>
+      <c r="K12" s="38"/>
+      <c r="L12" s="30"/>
+    </row>
+    <row r="13" spans="1:12" ht="75" customHeight="1">
+      <c r="A13" s="18" t="s">
+        <v>192</v>
+      </c>
+      <c r="B13" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="C13" s="33" t="s">
+        <v>193</v>
+      </c>
+      <c r="D13" s="34" t="s">
+        <v>194</v>
+      </c>
+      <c r="E13" s="35" t="s">
+        <v>159</v>
+      </c>
+      <c r="F13" s="34"/>
+      <c r="G13" s="35" t="s">
+        <v>195</v>
+      </c>
+      <c r="H13" s="39" t="s">
+        <v>196</v>
+      </c>
+      <c r="I13" s="35" t="s">
+        <v>185</v>
+      </c>
+      <c r="J13" s="35"/>
+      <c r="K13" s="38"/>
+      <c r="L13" s="34" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="75" customHeight="1">
+      <c r="A14" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="B14" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="C14" s="29" t="s">
+        <v>199</v>
+      </c>
+      <c r="D14" s="30" t="s">
+        <v>200</v>
+      </c>
+      <c r="E14" s="31" t="s">
+        <v>145</v>
+      </c>
+      <c r="F14" s="30" t="s">
+        <v>201</v>
+      </c>
+      <c r="G14" s="31" t="s">
+        <v>202</v>
+      </c>
+      <c r="H14" s="37" t="s">
+        <v>172</v>
+      </c>
+      <c r="I14" s="31" t="s">
+        <v>185</v>
+      </c>
+      <c r="J14" s="31"/>
+      <c r="K14" s="38"/>
+      <c r="L14" s="30"/>
+    </row>
+    <row r="15" spans="1:12" ht="75" customHeight="1">
+      <c r="A15" s="18" t="s">
+        <v>203</v>
+      </c>
+      <c r="B15" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="C15" s="33" t="s">
+        <v>204</v>
+      </c>
+      <c r="D15" s="34" t="s">
+        <v>205</v>
+      </c>
+      <c r="E15" s="35" t="s">
+        <v>206</v>
+      </c>
+      <c r="F15" s="34" t="s">
+        <v>207</v>
+      </c>
+      <c r="G15" s="35" t="s">
+        <v>208</v>
+      </c>
+      <c r="H15" s="39" t="s">
+        <v>196</v>
+      </c>
+      <c r="I15" s="35" t="s">
+        <v>185</v>
+      </c>
+      <c r="J15" s="35"/>
+      <c r="K15" s="38"/>
+      <c r="L15" s="34" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="75" customHeight="1">
+      <c r="A16" s="11" t="s">
+        <v>209</v>
+      </c>
+      <c r="B16" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="C16" s="29" t="s">
+        <v>210</v>
+      </c>
+      <c r="D16" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="E16" s="31" t="s">
+        <v>206</v>
+      </c>
+      <c r="F16" s="30" t="s">
+        <v>212</v>
+      </c>
+      <c r="G16" s="31" t="s">
+        <v>213</v>
+      </c>
+      <c r="H16" s="37" t="s">
+        <v>172</v>
+      </c>
+      <c r="I16" s="31" t="s">
+        <v>185</v>
+      </c>
+      <c r="J16" s="31"/>
+      <c r="K16" s="38"/>
+      <c r="L16" s="30"/>
+    </row>
+    <row r="17" spans="1:12" ht="75" customHeight="1">
+      <c r="A17" s="18" t="s">
+        <v>214</v>
+      </c>
+      <c r="B17" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="C17" s="33" t="s">
+        <v>215</v>
+      </c>
+      <c r="D17" s="34" t="s">
+        <v>216</v>
+      </c>
+      <c r="E17" s="35" t="s">
+        <v>159</v>
+      </c>
+      <c r="F17" s="34"/>
+      <c r="G17" s="35" t="s">
+        <v>217</v>
+      </c>
+      <c r="H17" s="32" t="s">
+        <v>148</v>
+      </c>
+      <c r="I17" s="35" t="s">
+        <v>185</v>
+      </c>
+      <c r="J17" s="35"/>
+      <c r="K17" s="38"/>
+      <c r="L17" s="34"/>
+    </row>
+    <row r="18" spans="1:12" ht="75" customHeight="1">
+      <c r="A18" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="B18" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="C18" s="29" t="s">
+        <v>219</v>
+      </c>
+      <c r="D18" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="E18" s="31" t="s">
+        <v>159</v>
+      </c>
+      <c r="F18" s="30"/>
+      <c r="G18" s="31" t="s">
+        <v>217</v>
+      </c>
+      <c r="H18" s="32" t="s">
+        <v>148</v>
+      </c>
+      <c r="I18" s="31" t="s">
+        <v>185</v>
+      </c>
+      <c r="J18" s="31"/>
+      <c r="K18" s="38"/>
+      <c r="L18" s="30"/>
+    </row>
+    <row r="19" spans="1:12" ht="75" customHeight="1">
+      <c r="A19" s="18" t="s">
+        <v>221</v>
+      </c>
+      <c r="B19" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="C19" s="33" t="s">
+        <v>222</v>
+      </c>
+      <c r="D19" s="34" t="s">
+        <v>223</v>
+      </c>
+      <c r="E19" s="35" t="s">
+        <v>145</v>
+      </c>
+      <c r="F19" s="34"/>
+      <c r="G19" s="35" t="s">
+        <v>224</v>
+      </c>
+      <c r="H19" s="32" t="s">
+        <v>148</v>
+      </c>
+      <c r="I19" s="35"/>
+      <c r="J19" s="35"/>
+      <c r="K19" s="38"/>
+      <c r="L19" s="34" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="75" customHeight="1">
+      <c r="A20" s="11" t="s">
+        <v>226</v>
+      </c>
+      <c r="B20" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="C20" s="29" t="s">
+        <v>227</v>
+      </c>
+      <c r="D20" s="30" t="s">
+        <v>228</v>
+      </c>
+      <c r="E20" s="31" t="s">
+        <v>145</v>
+      </c>
+      <c r="F20" s="30"/>
+      <c r="G20" s="31" t="s">
+        <v>224</v>
+      </c>
+      <c r="H20" s="32" t="s">
+        <v>148</v>
+      </c>
+      <c r="I20" s="31"/>
+      <c r="J20" s="31"/>
+      <c r="K20" s="38"/>
+      <c r="L20" s="30"/>
+    </row>
+    <row r="21" spans="1:12" ht="75" customHeight="1">
+      <c r="A21" s="18" t="s">
+        <v>229</v>
+      </c>
+      <c r="B21" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="C21" s="33" t="s">
+        <v>230</v>
+      </c>
+      <c r="D21" s="34" t="s">
+        <v>231</v>
+      </c>
+      <c r="E21" s="35" t="s">
+        <v>145</v>
+      </c>
+      <c r="F21" s="34"/>
+      <c r="G21" s="35" t="s">
+        <v>224</v>
+      </c>
+      <c r="H21" s="32" t="s">
+        <v>148</v>
+      </c>
+      <c r="I21" s="35"/>
+      <c r="J21" s="35"/>
+      <c r="K21" s="38"/>
+      <c r="L21" s="34"/>
+    </row>
+    <row r="22" spans="1:12" ht="75" customHeight="1">
+      <c r="A22" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="B22" s="40" t="s">
+        <v>233</v>
+      </c>
+      <c r="C22" s="41" t="s">
+        <v>234</v>
+      </c>
+      <c r="D22" s="42" t="s">
+        <v>235</v>
+      </c>
+      <c r="E22" s="43" t="s">
+        <v>145</v>
+      </c>
+      <c r="F22" s="42" t="s">
+        <v>236</v>
+      </c>
+      <c r="G22" s="43" t="s">
+        <v>237</v>
+      </c>
+      <c r="H22" s="32" t="s">
+        <v>148</v>
+      </c>
+      <c r="I22" s="43" t="s">
+        <v>238</v>
+      </c>
+      <c r="J22" s="43"/>
+      <c r="K22" s="36" t="s">
+        <v>154</v>
+      </c>
+      <c r="L22" s="42" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="75" customHeight="1">
+      <c r="A23" s="18" t="s">
+        <v>240</v>
+      </c>
+      <c r="B23" s="40" t="s">
+        <v>233</v>
+      </c>
+      <c r="C23" s="44" t="s">
+        <v>241</v>
+      </c>
+      <c r="D23" s="45" t="s">
+        <v>242</v>
+      </c>
+      <c r="E23" s="46" t="s">
+        <v>159</v>
+      </c>
+      <c r="F23" s="45" t="s">
+        <v>243</v>
+      </c>
+      <c r="G23" s="46" t="s">
+        <v>244</v>
+      </c>
+      <c r="H23" s="37" t="s">
+        <v>172</v>
+      </c>
+      <c r="I23" s="46" t="s">
+        <v>238</v>
+      </c>
+      <c r="J23" s="46" t="s">
+        <v>245</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="L23" s="45" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="75" customHeight="1">
+      <c r="A24" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="B24" s="40" t="s">
+        <v>233</v>
+      </c>
+      <c r="C24" s="41" t="s">
+        <v>248</v>
+      </c>
+      <c r="D24" s="42" t="s">
+        <v>249</v>
+      </c>
+      <c r="E24" s="43" t="s">
+        <v>250</v>
+      </c>
+      <c r="F24" s="42" t="s">
+        <v>251</v>
+      </c>
+      <c r="G24" s="43" t="s">
+        <v>252</v>
+      </c>
+      <c r="H24" s="37" t="s">
+        <v>172</v>
+      </c>
+      <c r="I24" s="43" t="s">
+        <v>238</v>
+      </c>
+      <c r="J24" s="43" t="s">
+        <v>253</v>
+      </c>
+      <c r="K24" s="38"/>
+      <c r="L24" s="42"/>
+    </row>
+    <row r="25" spans="1:12" ht="75" customHeight="1">
+      <c r="A25" s="18" t="s">
+        <v>254</v>
+      </c>
+      <c r="B25" s="40" t="s">
+        <v>233</v>
+      </c>
+      <c r="C25" s="44" t="s">
+        <v>255</v>
+      </c>
+      <c r="D25" s="45" t="s">
+        <v>256</v>
+      </c>
+      <c r="E25" s="46" t="s">
+        <v>257</v>
+      </c>
+      <c r="F25" s="45" t="s">
+        <v>258</v>
+      </c>
+      <c r="G25" s="46" t="s">
+        <v>252</v>
+      </c>
+      <c r="H25" s="37" t="s">
+        <v>172</v>
+      </c>
+      <c r="I25" s="46" t="s">
+        <v>259</v>
+      </c>
+      <c r="J25" s="46" t="s">
+        <v>260</v>
+      </c>
+      <c r="K25" s="38"/>
+      <c r="L25" s="45"/>
+    </row>
+    <row r="26" spans="1:12" ht="75" customHeight="1">
+      <c r="A26" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="B26" s="40" t="s">
+        <v>233</v>
+      </c>
+      <c r="C26" s="41" t="s">
+        <v>262</v>
+      </c>
+      <c r="D26" s="42" t="s">
+        <v>263</v>
+      </c>
+      <c r="E26" s="43" t="s">
+        <v>257</v>
+      </c>
+      <c r="F26" s="42" t="s">
+        <v>251</v>
+      </c>
+      <c r="G26" s="43" t="s">
+        <v>264</v>
+      </c>
+      <c r="H26" s="37" t="s">
+        <v>172</v>
+      </c>
+      <c r="I26" s="43" t="s">
+        <v>238</v>
+      </c>
+      <c r="J26" s="43" t="s">
+        <v>265</v>
+      </c>
+      <c r="K26" s="38"/>
+      <c r="L26" s="42"/>
+    </row>
+    <row r="27" spans="1:12" ht="75" customHeight="1">
+      <c r="A27" s="18" t="s">
+        <v>266</v>
+      </c>
+      <c r="B27" s="40" t="s">
+        <v>233</v>
+      </c>
+      <c r="C27" s="44" t="s">
+        <v>267</v>
+      </c>
+      <c r="D27" s="45" t="s">
+        <v>268</v>
+      </c>
+      <c r="E27" s="46" t="s">
+        <v>269</v>
+      </c>
+      <c r="F27" s="45" t="s">
+        <v>251</v>
+      </c>
+      <c r="G27" s="46" t="s">
+        <v>252</v>
+      </c>
+      <c r="H27" s="37" t="s">
+        <v>172</v>
+      </c>
+      <c r="I27" s="46" t="s">
+        <v>238</v>
+      </c>
+      <c r="J27" s="46" t="s">
+        <v>260</v>
+      </c>
+      <c r="K27" s="38"/>
+      <c r="L27" s="45" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="75" customHeight="1">
+      <c r="A28" s="11" t="s">
+        <v>271</v>
+      </c>
+      <c r="B28" s="40" t="s">
+        <v>233</v>
+      </c>
+      <c r="C28" s="41" t="s">
+        <v>272</v>
+      </c>
+      <c r="D28" s="42" t="s">
+        <v>273</v>
+      </c>
+      <c r="E28" s="43" t="s">
+        <v>274</v>
+      </c>
+      <c r="F28" s="42" t="s">
+        <v>275</v>
+      </c>
+      <c r="G28" s="43" t="s">
+        <v>252</v>
+      </c>
+      <c r="H28" s="37" t="s">
+        <v>172</v>
+      </c>
+      <c r="I28" s="43" t="s">
+        <v>259</v>
+      </c>
+      <c r="J28" s="43"/>
+      <c r="K28" s="38"/>
+      <c r="L28" s="42" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="75" customHeight="1">
+      <c r="A29" s="18" t="s">
+        <v>277</v>
+      </c>
+      <c r="B29" s="40" t="s">
+        <v>233</v>
+      </c>
+      <c r="C29" s="44" t="s">
+        <v>278</v>
+      </c>
+      <c r="D29" s="45" t="s">
+        <v>279</v>
+      </c>
+      <c r="E29" s="46" t="s">
+        <v>145</v>
+      </c>
+      <c r="F29" s="45" t="s">
+        <v>275</v>
+      </c>
+      <c r="G29" s="46" t="s">
+        <v>252</v>
+      </c>
+      <c r="H29" s="32" t="s">
+        <v>148</v>
+      </c>
+      <c r="I29" s="46" t="s">
+        <v>238</v>
+      </c>
+      <c r="J29" s="46"/>
+      <c r="K29" s="38"/>
+      <c r="L29" s="45" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="75" customHeight="1">
+      <c r="A30" s="11" t="s">
+        <v>281</v>
+      </c>
+      <c r="B30" s="40" t="s">
+        <v>233</v>
+      </c>
+      <c r="C30" s="41" t="s">
+        <v>282</v>
+      </c>
+      <c r="D30" s="42" t="s">
+        <v>283</v>
+      </c>
+      <c r="E30" s="43"/>
+      <c r="F30" s="42" t="s">
+        <v>275</v>
+      </c>
+      <c r="G30" s="43"/>
+      <c r="H30" s="38"/>
+      <c r="I30" s="43" t="s">
+        <v>259</v>
+      </c>
+      <c r="J30" s="43"/>
+      <c r="K30" s="38"/>
+      <c r="L30" s="42"/>
+    </row>
+    <row r="31" spans="1:12" ht="75" customHeight="1">
+      <c r="A31" s="18" t="s">
+        <v>284</v>
+      </c>
+      <c r="B31" s="40" t="s">
+        <v>233</v>
+      </c>
+      <c r="C31" s="44" t="s">
+        <v>285</v>
+      </c>
+      <c r="D31" s="45" t="s">
+        <v>286</v>
+      </c>
+      <c r="E31" s="46"/>
+      <c r="F31" s="45"/>
+      <c r="G31" s="46"/>
+      <c r="H31" s="32" t="s">
+        <v>148</v>
+      </c>
+      <c r="I31" s="46" t="s">
+        <v>238</v>
+      </c>
+      <c r="J31" s="46"/>
+      <c r="K31" s="38"/>
+      <c r="L31" s="45"/>
+    </row>
+    <row r="32" spans="1:12" ht="75" customHeight="1">
+      <c r="A32" s="11" t="s">
+        <v>287</v>
+      </c>
+      <c r="B32" s="40" t="s">
+        <v>233</v>
+      </c>
+      <c r="C32" s="41" t="s">
+        <v>288</v>
+      </c>
+      <c r="D32" s="42" t="s">
+        <v>289</v>
+      </c>
+      <c r="E32" s="43"/>
+      <c r="F32" s="42"/>
+      <c r="G32" s="43"/>
+      <c r="H32" s="32" t="s">
+        <v>148</v>
+      </c>
+      <c r="I32" s="43"/>
+      <c r="J32" s="43"/>
+      <c r="K32" s="38"/>
+      <c r="L32" s="42"/>
+    </row>
+    <row r="33" spans="1:12" ht="75" customHeight="1">
+      <c r="A33" s="18" t="s">
+        <v>290</v>
+      </c>
+      <c r="B33" s="40" t="s">
+        <v>233</v>
+      </c>
+      <c r="C33" s="44" t="s">
+        <v>291</v>
+      </c>
+      <c r="D33" s="45" t="s">
+        <v>292</v>
+      </c>
+      <c r="E33" s="46"/>
+      <c r="F33" s="45"/>
+      <c r="G33" s="46"/>
+      <c r="H33" s="32" t="s">
+        <v>148</v>
+      </c>
+      <c r="I33" s="46"/>
+      <c r="J33" s="46"/>
+      <c r="K33" s="38"/>
+      <c r="L33" s="45"/>
+    </row>
+    <row r="34" spans="1:12" ht="75" customHeight="1">
+      <c r="A34" s="11" t="s">
+        <v>293</v>
+      </c>
+      <c r="B34" s="40" t="s">
+        <v>233</v>
+      </c>
+      <c r="C34" s="41" t="s">
+        <v>294</v>
+      </c>
+      <c r="D34" s="42" t="s">
+        <v>295</v>
+      </c>
+      <c r="E34" s="43"/>
+      <c r="F34" s="42"/>
+      <c r="G34" s="43"/>
+      <c r="H34" s="32" t="s">
+        <v>148</v>
+      </c>
+      <c r="I34" s="43"/>
+      <c r="J34" s="43"/>
+      <c r="K34" s="38"/>
+      <c r="L34" s="42"/>
+    </row>
+    <row r="35" spans="1:12" ht="75" customHeight="1">
+      <c r="A35" s="18" t="s">
+        <v>296</v>
+      </c>
+      <c r="B35" s="40" t="s">
+        <v>233</v>
+      </c>
+      <c r="C35" s="44" t="s">
+        <v>297</v>
+      </c>
+      <c r="D35" s="45" t="s">
+        <v>298</v>
+      </c>
+      <c r="E35" s="46"/>
+      <c r="F35" s="45"/>
+      <c r="G35" s="46"/>
+      <c r="H35" s="38"/>
+      <c r="I35" s="46"/>
+      <c r="J35" s="46"/>
+      <c r="K35" s="38"/>
+      <c r="L35" s="45"/>
+    </row>
+    <row r="37" spans="1:12" ht="24" customHeight="1">
+      <c r="A37" s="22" t="s">
+        <v>124</v>
+      </c>
+      <c r="B37" s="22"/>
+      <c r="C37" s="22">
+        <f>COUNTA(A4:A35)&amp;" tasks"</f>
+        <v>0</v>
+      </c>
+      <c r="D37" s="22">
+        <f>COUNTIF(B4:B35,"Backlog FPTvn")&amp;" FPTvn | "&amp;COUNTIF(B4:B35,"Roadmap 18.5")&amp;" Roadmap"</f>
+        <v>0</v>
+      </c>
+      <c r="E37" s="22"/>
+      <c r="F37" s="22"/>
+      <c r="G37" s="22"/>
+      <c r="H37" s="22"/>
+      <c r="I37" s="22"/>
+      <c r="J37" s="22"/>
+      <c r="K37" s="22">
+        <f>COUNTIF(K4:K35,"In Progress")&amp;" In Progress | "&amp;COUNTIF(K4:K35,"To Do")&amp;" To Do"</f>
+        <v>0</v>
+      </c>
+      <c r="L37" s="22"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A37:B37"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="F4" r:id="rId1"/>
+    <hyperlink ref="F5" r:id="rId2"/>
+    <hyperlink ref="F6" r:id="rId3"/>
+    <hyperlink ref="F15" r:id="rId4"/>
+    <hyperlink ref="F16" r:id="rId5"/>
+    <hyperlink ref="F23" r:id="rId6"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2286,167 +4052,167 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1">
-      <c r="A1" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
+      <c r="A1" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
     </row>
     <row r="2" spans="1:7" ht="24" customHeight="1">
-      <c r="A2" s="27" t="s">
-        <v>31</v>
-      </c>
-      <c r="B2" s="27" t="s">
-        <v>132</v>
-      </c>
-      <c r="C2" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="D2" s="27" t="s">
-        <v>134</v>
-      </c>
-      <c r="E2" s="27" t="s">
-        <v>135</v>
-      </c>
-      <c r="F2" s="27" t="s">
-        <v>136</v>
-      </c>
-      <c r="G2" s="27" t="s">
-        <v>137</v>
+      <c r="A2" s="47" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" s="47" t="s">
+        <v>300</v>
+      </c>
+      <c r="C2" s="47" t="s">
+        <v>301</v>
+      </c>
+      <c r="D2" s="47" t="s">
+        <v>302</v>
+      </c>
+      <c r="E2" s="47" t="s">
+        <v>303</v>
+      </c>
+      <c r="F2" s="47" t="s">
+        <v>304</v>
+      </c>
+      <c r="G2" s="47" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="40" customHeight="1">
       <c r="A3" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="C3" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="C3" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="G3" s="11" t="s">
-        <v>142</v>
+      <c r="D3" s="10" t="s">
+        <v>307</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>308</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>309</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="40" customHeight="1">
-      <c r="A4" s="28" t="s">
-        <v>57</v>
-      </c>
-      <c r="B4" s="29" t="s">
-        <v>138</v>
-      </c>
-      <c r="C4" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="D4" s="29" t="s">
-        <v>144</v>
-      </c>
-      <c r="E4" s="30" t="s">
-        <v>145</v>
-      </c>
-      <c r="F4" s="31" t="s">
-        <v>146</v>
-      </c>
-      <c r="G4" s="30" t="s">
-        <v>147</v>
+      <c r="A4" s="48" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4" s="49" t="s">
+        <v>306</v>
+      </c>
+      <c r="C4" s="49" t="s">
+        <v>311</v>
+      </c>
+      <c r="D4" s="49" t="s">
+        <v>312</v>
+      </c>
+      <c r="E4" s="50" t="s">
+        <v>313</v>
+      </c>
+      <c r="F4" s="51" t="s">
+        <v>314</v>
+      </c>
+      <c r="G4" s="50" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="40" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="G5" s="11" t="s">
-        <v>151</v>
+        <v>75</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>318</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>314</v>
+      </c>
+      <c r="G5" s="13" t="s">
+        <v>319</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="40" customHeight="1">
-      <c r="A6" s="28" t="s">
-        <v>95</v>
-      </c>
-      <c r="B6" s="29" t="s">
-        <v>138</v>
-      </c>
-      <c r="C6" s="29" t="s">
-        <v>152</v>
-      </c>
-      <c r="D6" s="29" t="s">
-        <v>153</v>
-      </c>
-      <c r="E6" s="30" t="s">
-        <v>154</v>
-      </c>
-      <c r="F6" s="31" t="s">
-        <v>155</v>
-      </c>
-      <c r="G6" s="30" t="s">
-        <v>156</v>
+      <c r="A6" s="48" t="s">
+        <v>94</v>
+      </c>
+      <c r="B6" s="49" t="s">
+        <v>306</v>
+      </c>
+      <c r="C6" s="49" t="s">
+        <v>191</v>
+      </c>
+      <c r="D6" s="49" t="s">
+        <v>320</v>
+      </c>
+      <c r="E6" s="50" t="s">
+        <v>321</v>
+      </c>
+      <c r="F6" s="51" t="s">
+        <v>322</v>
+      </c>
+      <c r="G6" s="50" t="s">
+        <v>323</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="40" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="G7" s="11" t="s">
-        <v>159</v>
+        <v>123</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>324</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>324</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>324</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>325</v>
+      </c>
+      <c r="G7" s="13" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="26" customHeight="1">
-      <c r="A9" s="32" t="s">
-        <v>160</v>
-      </c>
-      <c r="B9" s="32"/>
-      <c r="C9" s="32"/>
-      <c r="D9" s="32"/>
-      <c r="E9" s="32"/>
-      <c r="F9" s="32" t="s">
-        <v>161</v>
-      </c>
-      <c r="G9" s="32" t="s">
-        <v>162</v>
+      <c r="A9" s="22" t="s">
+        <v>327</v>
+      </c>
+      <c r="B9" s="22"/>
+      <c r="C9" s="22"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="22" t="s">
+        <v>328</v>
+      </c>
+      <c r="G9" s="22" t="s">
+        <v>329</v>
       </c>
     </row>
   </sheetData>
@@ -2458,7 +4224,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2469,98 +4235,98 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="30" customHeight="1">
-      <c r="A1" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
+      <c r="A1" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
     </row>
     <row r="2" spans="1:3" ht="22" customHeight="1">
-      <c r="A2" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>165</v>
+      <c r="A2" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>331</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="26" customHeight="1">
-      <c r="A3" s="33" t="s">
-        <v>166</v>
-      </c>
-      <c r="B3" s="34" t="s">
-        <v>167</v>
-      </c>
-      <c r="C3" s="35" t="s">
-        <v>168</v>
+      <c r="A3" s="26" t="s">
+        <v>333</v>
+      </c>
+      <c r="B3" s="52" t="s">
+        <v>334</v>
+      </c>
+      <c r="C3" s="53" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="26" customHeight="1">
-      <c r="A4" s="33" t="s">
-        <v>169</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>170</v>
-      </c>
-      <c r="C4" s="36" t="s">
-        <v>171</v>
+      <c r="A4" s="26" t="s">
+        <v>336</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>337</v>
+      </c>
+      <c r="C4" s="54" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="26" customHeight="1">
-      <c r="A5" s="33" t="s">
-        <v>172</v>
-      </c>
-      <c r="B5" s="34" t="s">
-        <v>173</v>
-      </c>
-      <c r="C5" s="35" t="s">
-        <v>174</v>
+      <c r="A5" s="26" t="s">
+        <v>339</v>
+      </c>
+      <c r="B5" s="52" t="s">
+        <v>340</v>
+      </c>
+      <c r="C5" s="53" t="s">
+        <v>341</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="26" customHeight="1">
-      <c r="A6" s="33" t="s">
-        <v>175</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="C6" s="36" t="s">
-        <v>177</v>
+      <c r="A6" s="26" t="s">
+        <v>342</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>343</v>
+      </c>
+      <c r="C6" s="54" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="26" customHeight="1">
-      <c r="A7" s="33" t="s">
-        <v>178</v>
-      </c>
-      <c r="B7" s="34" t="s">
-        <v>179</v>
-      </c>
-      <c r="C7" s="35" t="s">
-        <v>180</v>
+      <c r="A7" s="26" t="s">
+        <v>345</v>
+      </c>
+      <c r="B7" s="52" t="s">
+        <v>346</v>
+      </c>
+      <c r="C7" s="53" t="s">
+        <v>347</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="26" customHeight="1">
-      <c r="A8" s="33" t="s">
-        <v>181</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="C8" s="36" t="s">
-        <v>183</v>
+      <c r="A8" s="26" t="s">
+        <v>348</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>349</v>
+      </c>
+      <c r="C8" s="54" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="26" customHeight="1">
-      <c r="A9" s="33" t="s">
-        <v>184</v>
-      </c>
-      <c r="B9" s="34" t="s">
-        <v>185</v>
-      </c>
-      <c r="C9" s="35" t="s">
-        <v>186</v>
+      <c r="A9" s="26" t="s">
+        <v>351</v>
+      </c>
+      <c r="B9" s="52" t="s">
+        <v>352</v>
+      </c>
+      <c r="C9" s="53" t="s">
+        <v>353</v>
       </c>
     </row>
   </sheetData>
@@ -2571,7 +4337,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L10"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2580,170 +4346,166 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="30" customHeight="1">
-      <c r="A1" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
+      <c r="A1" s="8" t="s">
+        <v>354</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
     </row>
     <row r="2" spans="1:12" ht="26" customHeight="1">
-      <c r="A2" s="37" t="s">
-        <v>40</v>
-      </c>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="38" t="s">
-        <v>196</v>
-      </c>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="39" t="s">
-        <v>197</v>
-      </c>
-      <c r="H2" s="39"/>
-      <c r="I2" s="39"/>
-      <c r="J2" s="40" t="s">
-        <v>198</v>
-      </c>
-      <c r="K2" s="40"/>
-      <c r="L2" s="40"/>
+      <c r="A2" s="55" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="56" t="s">
+        <v>154</v>
+      </c>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="57" t="s">
+        <v>361</v>
+      </c>
+      <c r="H2" s="57"/>
+      <c r="I2" s="57"/>
+      <c r="J2" s="58" t="s">
+        <v>362</v>
+      </c>
+      <c r="K2" s="58"/>
+      <c r="L2" s="58"/>
     </row>
     <row r="3" spans="1:12" ht="50" customHeight="1">
-      <c r="A3" s="41" t="s">
-        <v>188</v>
-      </c>
-      <c r="B3" s="41"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="43"/>
-      <c r="I3" s="43"/>
-      <c r="J3" s="44"/>
-      <c r="K3" s="44"/>
-      <c r="L3" s="44"/>
+      <c r="A3" s="59" t="s">
+        <v>355</v>
+      </c>
+      <c r="B3" s="59"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="60"/>
+      <c r="E3" s="60"/>
+      <c r="F3" s="60"/>
+      <c r="G3" s="61"/>
+      <c r="H3" s="61"/>
+      <c r="I3" s="61"/>
+      <c r="J3" s="62"/>
+      <c r="K3" s="62"/>
+      <c r="L3" s="62"/>
     </row>
     <row r="4" spans="1:12" ht="50" customHeight="1">
-      <c r="A4" s="41" t="s">
-        <v>189</v>
-      </c>
-      <c r="B4" s="41"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="42"/>
-      <c r="E4" s="42"/>
-      <c r="F4" s="42"/>
-      <c r="G4" s="43"/>
-      <c r="H4" s="43"/>
-      <c r="I4" s="43"/>
-      <c r="J4" s="44"/>
-      <c r="K4" s="44"/>
-      <c r="L4" s="44"/>
+      <c r="A4" s="59" t="s">
+        <v>356</v>
+      </c>
+      <c r="B4" s="59"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="60"/>
+      <c r="E4" s="60"/>
+      <c r="F4" s="60"/>
+      <c r="G4" s="61"/>
+      <c r="H4" s="61"/>
+      <c r="I4" s="61"/>
+      <c r="J4" s="62"/>
+      <c r="K4" s="62"/>
+      <c r="L4" s="62"/>
     </row>
     <row r="5" spans="1:12" ht="50" customHeight="1">
-      <c r="A5" s="41" t="s">
-        <v>190</v>
-      </c>
-      <c r="B5" s="41"/>
-      <c r="C5" s="41"/>
-      <c r="D5" s="42"/>
-      <c r="E5" s="42"/>
-      <c r="F5" s="42"/>
-      <c r="G5" s="43"/>
-      <c r="H5" s="43"/>
-      <c r="I5" s="43"/>
-      <c r="J5" s="44"/>
-      <c r="K5" s="44"/>
-      <c r="L5" s="44"/>
+      <c r="A5" s="59" t="s">
+        <v>357</v>
+      </c>
+      <c r="B5" s="59"/>
+      <c r="C5" s="59"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="61"/>
+      <c r="J5" s="62"/>
+      <c r="K5" s="62"/>
+      <c r="L5" s="62"/>
     </row>
     <row r="6" spans="1:12" ht="50" customHeight="1">
-      <c r="A6" s="41" t="s">
-        <v>191</v>
-      </c>
-      <c r="B6" s="41"/>
-      <c r="C6" s="41"/>
-      <c r="D6" s="42"/>
-      <c r="E6" s="42"/>
-      <c r="F6" s="42"/>
-      <c r="G6" s="43"/>
-      <c r="H6" s="43"/>
-      <c r="I6" s="43"/>
-      <c r="J6" s="44"/>
-      <c r="K6" s="44"/>
-      <c r="L6" s="44"/>
+      <c r="A6" s="59" t="s">
+        <v>358</v>
+      </c>
+      <c r="B6" s="59"/>
+      <c r="C6" s="59"/>
+      <c r="D6" s="60"/>
+      <c r="E6" s="60"/>
+      <c r="F6" s="60"/>
+      <c r="G6" s="61"/>
+      <c r="H6" s="61"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="62"/>
+      <c r="K6" s="62"/>
+      <c r="L6" s="62"/>
     </row>
     <row r="7" spans="1:12" ht="50" customHeight="1">
-      <c r="A7" s="41" t="s">
-        <v>192</v>
-      </c>
-      <c r="B7" s="41"/>
-      <c r="C7" s="41"/>
-      <c r="D7" s="42"/>
-      <c r="E7" s="42"/>
-      <c r="F7" s="42"/>
-      <c r="G7" s="43"/>
-      <c r="H7" s="43"/>
-      <c r="I7" s="43"/>
-      <c r="J7" s="44"/>
-      <c r="K7" s="44"/>
-      <c r="L7" s="44"/>
+      <c r="A7" s="59" t="s">
+        <v>359</v>
+      </c>
+      <c r="B7" s="59"/>
+      <c r="C7" s="59"/>
+      <c r="D7" s="60"/>
+      <c r="E7" s="60"/>
+      <c r="F7" s="60"/>
+      <c r="G7" s="61"/>
+      <c r="H7" s="61"/>
+      <c r="I7" s="61"/>
+      <c r="J7" s="62"/>
+      <c r="K7" s="62"/>
+      <c r="L7" s="62"/>
     </row>
     <row r="8" spans="1:12" ht="50" customHeight="1">
-      <c r="A8" s="41" t="s">
-        <v>193</v>
-      </c>
-      <c r="B8" s="41"/>
-      <c r="C8" s="41"/>
-      <c r="D8" s="42"/>
-      <c r="E8" s="42"/>
-      <c r="F8" s="42"/>
-      <c r="G8" s="43"/>
-      <c r="H8" s="43"/>
-      <c r="I8" s="43"/>
-      <c r="J8" s="44"/>
-      <c r="K8" s="44"/>
-      <c r="L8" s="44"/>
+      <c r="A8" s="59" t="s">
+        <v>360</v>
+      </c>
+      <c r="B8" s="59"/>
+      <c r="C8" s="59"/>
+      <c r="D8" s="60"/>
+      <c r="E8" s="60"/>
+      <c r="F8" s="60"/>
+      <c r="G8" s="61"/>
+      <c r="H8" s="61"/>
+      <c r="I8" s="61"/>
+      <c r="J8" s="62"/>
+      <c r="K8" s="62"/>
+      <c r="L8" s="62"/>
     </row>
     <row r="9" spans="1:12" ht="50" customHeight="1">
-      <c r="A9" s="41" t="s">
-        <v>194</v>
-      </c>
-      <c r="B9" s="41"/>
-      <c r="C9" s="41"/>
-      <c r="D9" s="42"/>
-      <c r="E9" s="42"/>
-      <c r="F9" s="42"/>
-      <c r="G9" s="43"/>
-      <c r="H9" s="43"/>
-      <c r="I9" s="43"/>
-      <c r="J9" s="44"/>
-      <c r="K9" s="44"/>
-      <c r="L9" s="44"/>
+      <c r="A9" s="63"/>
+      <c r="B9" s="63"/>
+      <c r="C9" s="63"/>
+      <c r="D9" s="60"/>
+      <c r="E9" s="60"/>
+      <c r="F9" s="60"/>
+      <c r="G9" s="61"/>
+      <c r="H9" s="61"/>
+      <c r="I9" s="61"/>
+      <c r="J9" s="62"/>
+      <c r="K9" s="62"/>
+      <c r="L9" s="62"/>
     </row>
     <row r="10" spans="1:12" ht="50" customHeight="1">
-      <c r="A10" s="41" t="s">
-        <v>195</v>
-      </c>
-      <c r="B10" s="41"/>
-      <c r="C10" s="41"/>
-      <c r="D10" s="42"/>
-      <c r="E10" s="42"/>
-      <c r="F10" s="42"/>
-      <c r="G10" s="43"/>
-      <c r="H10" s="43"/>
-      <c r="I10" s="43"/>
-      <c r="J10" s="44"/>
-      <c r="K10" s="44"/>
-      <c r="L10" s="44"/>
+      <c r="A10" s="63"/>
+      <c r="B10" s="63"/>
+      <c r="C10" s="63"/>
+      <c r="D10" s="60"/>
+      <c r="E10" s="60"/>
+      <c r="F10" s="60"/>
+      <c r="G10" s="61"/>
+      <c r="H10" s="61"/>
+      <c r="I10" s="61"/>
+      <c r="J10" s="62"/>
+      <c r="K10" s="62"/>
+      <c r="L10" s="62"/>
     </row>
   </sheetData>
   <mergeCells count="37">
